--- a/artfynd/A 39032-2021 artfynd.xlsx
+++ b/artfynd/A 39032-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39032-2021 artfynd.xlsx
+++ b/artfynd/A 39032-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103956237</v>
+        <v>103956238</v>
       </c>
       <c r="B2" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655410.1217086981</v>
+        <v>655410</v>
       </c>
       <c r="R2" t="n">
-        <v>7193704.068388744</v>
+        <v>7193705</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103956238</v>
+        <v>103956237</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655410.0776394268</v>
+        <v>655410</v>
       </c>
       <c r="R3" t="n">
-        <v>7193704.919024333</v>
+        <v>7193704</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103956241</v>
+        <v>103956240</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655454.4095285215</v>
+        <v>655444</v>
       </c>
       <c r="R4" t="n">
-        <v>7193681.628385903</v>
+        <v>7193690</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103956240</v>
+        <v>103956196</v>
       </c>
       <c r="B5" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655444.556188324</v>
+        <v>655087</v>
       </c>
       <c r="R5" t="n">
-        <v>7193690.499960907</v>
+        <v>7193646</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,12 +1082,7 @@
         <v>103956239</v>
       </c>
       <c r="B6" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,12 +1099,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655436.2079094527</v>
+        <v>655436</v>
       </c>
       <c r="R6" t="n">
-        <v>7193703.287663319</v>
+        <v>7193703</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103956196</v>
+        <v>103956241</v>
       </c>
       <c r="B7" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655086.9369534862</v>
+        <v>655454</v>
       </c>
       <c r="R7" t="n">
-        <v>7193645.549440031</v>
+        <v>7193681</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,19 +1248,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 39032-2021 artfynd.xlsx
+++ b/artfynd/A 39032-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103956238</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103956237</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103956240</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103956196</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103956239</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,8 +1308,21 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103956241</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>